--- a/artfynd/A 17081-2026 artfynd.xlsx
+++ b/artfynd/A 17081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121285086</v>
+        <v>121285069</v>
       </c>
       <c r="B2" t="n">
-        <v>6267</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105336</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521285</v>
+        <v>520698</v>
       </c>
       <c r="R2" t="n">
-        <v>6714502</v>
+        <v>6714575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121285088</v>
+        <v>121285078</v>
       </c>
       <c r="B3" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520895</v>
+        <v>520794</v>
       </c>
       <c r="R3" t="n">
-        <v>6714419</v>
+        <v>6714588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +882,7 @@
         <v>121285071</v>
       </c>
       <c r="B4" t="n">
-        <v>91130</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121285069</v>
+        <v>121285081</v>
       </c>
       <c r="B5" t="n">
-        <v>78648</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520698</v>
+        <v>520995</v>
       </c>
       <c r="R5" t="n">
-        <v>6714575</v>
+        <v>6714376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121285089</v>
+        <v>121285074</v>
       </c>
       <c r="B6" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521334</v>
+        <v>520903</v>
       </c>
       <c r="R6" t="n">
-        <v>6714556</v>
+        <v>6714599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,12 +1188,7 @@
         <v>121285082</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121285077</v>
+        <v>121285086</v>
       </c>
       <c r="B8" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>105336</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520859</v>
+        <v>521285</v>
       </c>
       <c r="R8" t="n">
-        <v>6714594</v>
+        <v>6714502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121285075</v>
+        <v>121285073</v>
       </c>
       <c r="B9" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,34 +1400,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520519</v>
+        <v>520766</v>
       </c>
       <c r="R9" t="n">
-        <v>6714510</v>
+        <v>6714600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,6 +1482,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,15 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121285078</v>
+        <v>121285079</v>
       </c>
       <c r="B10" t="n">
-        <v>92001</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,34 +1512,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520794</v>
+        <v>520714</v>
       </c>
       <c r="R10" t="n">
-        <v>6714588</v>
+        <v>6714610</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,6 +1594,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1638,15 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121285076</v>
+        <v>121285080</v>
       </c>
       <c r="B11" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,34 +1624,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520472</v>
+        <v>520756</v>
       </c>
       <c r="R11" t="n">
-        <v>6714511</v>
+        <v>6714531</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,6 +1706,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1745,15 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121285087</v>
+        <v>121285083</v>
       </c>
       <c r="B12" t="n">
-        <v>97064</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1736,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521072</v>
+        <v>521002</v>
       </c>
       <c r="R12" t="n">
-        <v>6714443</v>
+        <v>6714371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,6 +1818,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1852,15 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121285073</v>
+        <v>121285084</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520766</v>
+        <v>521016</v>
       </c>
       <c r="R13" t="n">
-        <v>6714600</v>
+        <v>6714408</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,15 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121285079</v>
+        <v>121285085</v>
       </c>
       <c r="B14" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520714</v>
+        <v>521322</v>
       </c>
       <c r="R14" t="n">
-        <v>6714610</v>
+        <v>6714527</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,15 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121285085</v>
+        <v>121285070</v>
       </c>
       <c r="B15" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2102,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>214803</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521322</v>
+        <v>520509</v>
       </c>
       <c r="R15" t="n">
-        <v>6714527</v>
+        <v>6714485</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121285080</v>
+        <v>121285075</v>
       </c>
       <c r="B16" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2219,43 +2184,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520756</v>
+        <v>520519</v>
       </c>
       <c r="R16" t="n">
-        <v>6714531</v>
+        <v>6714510</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,7 +2257,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2320,15 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121285084</v>
+        <v>121285076</v>
       </c>
       <c r="B17" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,43 +2286,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521016</v>
+        <v>520472</v>
       </c>
       <c r="R17" t="n">
-        <v>6714408</v>
+        <v>6714511</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,7 +2359,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2437,15 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121285070</v>
+        <v>121285077</v>
       </c>
       <c r="B18" t="n">
-        <v>39847</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,43 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>214803</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Repbäcken till Grycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520509</v>
+        <v>520859</v>
       </c>
       <c r="R18" t="n">
-        <v>6714485</v>
+        <v>6714594</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2535,7 +2461,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2551,6 +2476,312 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121285087</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Repbäcken till Grycksbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521072</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6714443</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Väg &amp; Miljö AB, Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121285088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Repbäcken till Grycksbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>520895</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6714419</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Väg &amp; Miljö AB, Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121285089</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Repbäcken till Grycksbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521334</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6714556</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Väg &amp; Miljö AB, Naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17081-2026 artfynd.xlsx
+++ b/artfynd/A 17081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285069</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285078</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285081</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285074</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285082</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285086</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285073</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285079</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285080</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285083</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285084</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2058,6 +2123,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285070</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285075</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285076</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,6 +2561,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285077</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285087</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285088</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,8 +2882,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121285089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>